--- a/audits/transitions-workflow-audit/Transitions_Master_Rules.xlsx
+++ b/audits/transitions-workflow-audit/Transitions_Master_Rules.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -517,7 +518,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 10:43 UTC (saved settings snapshot)</t>
+          <t>The live settings on 2026-10-13 (read-only snapshot taken at 10:43 UTC).</t>
         </is>
       </c>
     </row>
@@ -644,12 +645,24 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Planned change</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Go-Live Execution Tasks (+SubTask) (1866664222): on 2026-10-06 the Transitions queue (13519270) was set on its 5 Create task actions (revision 54 -&gt; 60). This was a planned change (confirmed by Cherine on 2026-10-06), so it is part of this baseline, not a change to report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Change log</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13: file created.</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13: file created from the live settings on 2026-10-13.</t>
         </is>
       </c>
     </row>

--- a/audits/transitions-workflow-audit/Transitions_Master_Rules.xlsx
+++ b/audits/transitions-workflow-audit/Transitions_Master_Rules.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -518,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The live settings on 2026-10-13 (read-only snapshot taken at 10:43 UTC).</t>
+          <t>The live settings on 2026-10-13 (read-only snapshot taken at 10:43 UTC), except Closed Won (1670039203): its row holds its settings before the 8 Oct edit (revision 13), because that edit is not confirmed.</t>
         </is>
       </c>
     </row>
@@ -663,6 +662,18 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2026-10-13: file created from the live settings on 2026-10-13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Change log</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13: updated 1670039203. Closed Won (1670039203) row set to its settings before the 8 Oct edit (revision 13, read 2026-10-06). The 8 Oct edit (revision 14: no longer copies the deal's companies onto the ticket) is not confirmed (Cherine, 2026-10-13), so it is reported as a change, not yet confirmed (Waiting on Cherine W-4).</t>
         </is>
       </c>
     </row>
@@ -821,7 +832,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>When a deal reaches Closed won (White Label Storage SALES pipeline), creates one Onboarding Pipeline ticket in UNASSIGNED named after the deal, owned by Elizabeth Airey, linked to the deal and the deal's contacts. Creates no tasks.</t>
+          <t>When a deal reaches Closed won (White Label Storage SALES pipeline), creates one Onboarding Pipeline ticket in UNASSIGNED named after the deal, owned by Elizabeth Airey, linked to the deal, the deal's contacts and the deal's companies (label "Transitions"). Creates no tasks. Baseline = revision 13; the 8 Oct edit (revision 14) is not confirmed.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -856,7 +867,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>(start): Create record - {"associations": [{"target": {"associationCategory": "HUBSPOT_DEFINED", "associationTypeId": 16}, "value": {"sourceSpec": {"associationCategory": "HUBSPOT_DEFINED", "associationTypeId": 3}, "type": "C</t>
+          <t>(start): Create record - create a Ticket; set Ticket name = {{ enrolled_object.dealname }}; Ticket status = UNASSIGNED; Ticket owner = Elizabeth Airey; links: Ticket -&gt; Contact (all): copied from the enrolled record's Deal -&gt; Contact (all); Ticket -&gt; Company, label "Transitions": copied from the enrolled record's Deal -&gt; Company (all); Ticket -&gt; Deal (all): the enrolled record</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -881,12 +892,12 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-08 11:35:19 UTC</t>
+          <t>2026-07-15 11:06:08 UTC</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr"/>
@@ -1615,7 +1626,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"actions":[{"actionId":"1","actionTypeId":"0-14","actionTypeVersion":0,"fields":{"associations":[{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":16},"value":{"sourceSpec":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":3},"type":"COPY_ASSOCIATION"}},{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":28},"value":{"type":"ENROLLED_OBJECT"}}],"object_type_id":"0-5","properties":[{"targetProperty":"subject","value":{"staticValue":"{{ enrolled_object.dealname }}","type":"STATIC_VALUE"}},{"targetProperty":"hs_pipeline_stage","value":{"staticValue":"1100007030","type":"STATIC_VALUE"}},{"targetProperty":"hubspot_owner_id","value":{"staticValue":"81929768","type":"STATIC_VALUE"}}],"use_explicit_associations":"true"},"type":"SINGLE_CONNECTION"}],"blockedDates":[],"enrollmentCriteria":{"listFilterBranch":{"filterBranchOperator":"OR","filterBranchType":"OR","filterBranches":[{"filterBranchOperator":"AND","filterBranchType":"AND","filterBranches":[],"filters":[{"filterType":"PROPERTY","operation":{"includeObjectsWithNoValueSet":false,"operationType":"ENUMERATION","operator":"IS_ANY_OF","values":["150102819"]},"property":"dealstage"}]}],"filters":[]},"reEnrollmentTriggersFilterBranches":[],"shouldReEnroll":false,"type":"LIST_BASED","unEnrollObjectsNotMeetingCriteria":false},"id":"1670039203","isEnabled":true,"name":"Closed Won | Create Ticket in INITIAL SETUP - UNASSIGNED","objectTypeId":"0-3","revisionId":"14","startActionId":"1","timeWindows":[],"updatedAt":"2026-10-08T11:35:19.692Z"}</t>
+          <t>{"actions":[{"actionId":"1","actionTypeId":"0-14","actionTypeVersion":0,"fields":{"associations":[{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":16},"value":{"sourceSpec":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":3},"type":"COPY_ASSOCIATION"}},{"target":{"associationCategory":"USER_DEFINED","associationTypeId":70},"value":{"sourceSpec":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":341},"type":"COPY_ASSOCIATION"}},{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":28},"value":{"type":"ENROLLED_OBJECT"}}],"object_type_id":"0-5","properties":[{"targetProperty":"subject","value":{"staticValue":"{{ enrolled_object.dealname }}","type":"STATIC_VALUE"}},{"targetProperty":"hs_pipeline_stage","value":{"staticValue":"1100007030","type":"STATIC_VALUE"}},{"targetProperty":"hubspot_owner_id","value":{"staticValue":"81929768","type":"STATIC_VALUE"}}],"use_explicit_associations":"true"},"type":"SINGLE_CONNECTION"}],"blockedDates":[],"enrollmentCriteria":{"listFilterBranch":{"filterBranchOperator":"OR","filterBranchType":"OR","filterBranches":[{"filterBranchOperator":"AND","filterBranchType":"AND","filterBranches":[],"filters":[{"filterType":"PROPERTY","operation":{"includeObjectsWithNoValueSet":false,"operationType":"ENUMERATION","operator":"IS_ANY_OF","values":["150102819"]},"property":"dealstage"}]}],"filters":[]},"reEnrollmentTriggersFilterBranches":[],"shouldReEnroll":false,"type":"LIST_BASED","unEnrollObjectsNotMeetingCriteria":false},"id":"1670039203","isEnabled":true,"name":"Closed Won | Create Ticket in INITIAL SETUP - UNASSIGNED","objectTypeId":"0-3","revisionId":"13","startActionId":"1","timeWindows":[],"updatedAt":"2026-07-15T11:06:08.153Z"}</t>
         </is>
       </c>
     </row>

--- a/audits/transitions-workflow-audit/Transitions_Master_Rules.xlsx
+++ b/audits/transitions-workflow-audit/Transitions_Master_Rules.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The live settings on 2026-10-13 (read-only snapshot taken at 10:43 UTC), except Closed Won (1670039203): its row holds its settings before the 8 Oct edit (revision 13), because that edit is not confirmed.</t>
+          <t>The live settings on 2026-10-13 (read-only snapshot taken at 10:43 UTC). Closed Won (1670039203) was updated to revision 14 on 2026-10-20 after Cherine confirmed the 8 Oct edit was planned.</t>
         </is>
       </c>
     </row>
@@ -674,6 +674,18 @@
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2026-10-13: updated 1670039203. Closed Won (1670039203) row set to its settings before the 8 Oct edit (revision 13, read 2026-10-06). The 8 Oct edit (revision 14: no longer copies the deal's companies onto the ticket) is not confirmed (Cherine, 2026-10-13), so it is reported as a change, not yet confirmed (Waiting on Cherine W-4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Change log</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20: updated 1670039203. Planned change confirmed by Cherine on 2026-10-20 (W-4): the 8 Oct edit (revision 13 -&gt; 14) removed the copy of the deal's companies onto the ticket on purpose, because the facility doesn't exist yet when the deal closes.</t>
         </is>
       </c>
     </row>
@@ -832,12 +844,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>When a deal reaches Closed won (White Label Storage SALES pipeline), creates one Onboarding Pipeline ticket in UNASSIGNED named after the deal, owned by Elizabeth Airey, linked to the deal, the deal's contacts and the deal's companies (label "Transitions"). Creates no tasks. Baseline = revision 13; the 8 Oct edit (revision 14) is not confirmed.</t>
+          <t>When a deal reaches Closed won (White Label Storage SALES pipeline), creates one Onboarding Pipeline ticket in UNASSIGNED named after the deal, owned by Elizabeth Airey, linked to the deal and the deal's contacts. It adds no company on purpose: the facility doesn't exist yet (it's created later by Create Facility and linked to the ticket by hand). Creates no tasks.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Filter-based: Deal Stage is any of Closed won (White Label Storage SALES)</t>
+          <t>Filter-based: dealstage is any of Closed won (White Label Storage SALES)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -867,7 +879,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>(start): Create record - create a Ticket; set Ticket name = {{ enrolled_object.dealname }}; Ticket status = UNASSIGNED; Ticket owner = Elizabeth Airey; links: Ticket -&gt; Contact (all): copied from the enrolled record's Deal -&gt; Contact (all); Ticket -&gt; Company, label "Transitions": copied from the enrolled record's Deal -&gt; Company (all); Ticket -&gt; Deal (all): the enrolled record</t>
+          <t>(start): Create record - create a Ticket; set Ticket name = {{ enrolled_object.dealname }}; Ticket status = UNASSIGNED; Ticket owner = Elizabeth Airey; links: Ticket -&gt; Contact (all): copied from the enrolled record's Deal -&gt; Contact (all); Ticket -&gt; Deal (all): the enrolled record</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -892,12 +904,12 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15 11:06:08 UTC</t>
+          <t>2026-10-08 11:35:19 UTC</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr"/>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"actions":[{"actionId":"1","actionTypeId":"0-14","actionTypeVersion":0,"fields":{"associations":[{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":16},"value":{"sourceSpec":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":3},"type":"COPY_ASSOCIATION"}},{"target":{"associationCategory":"USER_DEFINED","associationTypeId":70},"value":{"sourceSpec":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":341},"type":"COPY_ASSOCIATION"}},{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":28},"value":{"type":"ENROLLED_OBJECT"}}],"object_type_id":"0-5","properties":[{"targetProperty":"subject","value":{"staticValue":"{{ enrolled_object.dealname }}","type":"STATIC_VALUE"}},{"targetProperty":"hs_pipeline_stage","value":{"staticValue":"1100007030","type":"STATIC_VALUE"}},{"targetProperty":"hubspot_owner_id","value":{"staticValue":"81929768","type":"STATIC_VALUE"}}],"use_explicit_associations":"true"},"type":"SINGLE_CONNECTION"}],"blockedDates":[],"enrollmentCriteria":{"listFilterBranch":{"filterBranchOperator":"OR","filterBranchType":"OR","filterBranches":[{"filterBranchOperator":"AND","filterBranchType":"AND","filterBranches":[],"filters":[{"filterType":"PROPERTY","operation":{"includeObjectsWithNoValueSet":false,"operationType":"ENUMERATION","operator":"IS_ANY_OF","values":["150102819"]},"property":"dealstage"}]}],"filters":[]},"reEnrollmentTriggersFilterBranches":[],"shouldReEnroll":false,"type":"LIST_BASED","unEnrollObjectsNotMeetingCriteria":false},"id":"1670039203","isEnabled":true,"name":"Closed Won | Create Ticket in INITIAL SETUP - UNASSIGNED","objectTypeId":"0-3","revisionId":"13","startActionId":"1","timeWindows":[],"updatedAt":"2026-07-15T11:06:08.153Z"}</t>
+          <t>{"actions":[{"actionId":"1","actionTypeId":"0-14","actionTypeVersion":0,"fields":{"associations":[{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":16},"value":{"sourceSpec":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":3},"type":"COPY_ASSOCIATION"}},{"target":{"associationCategory":"HUBSPOT_DEFINED","associationTypeId":28},"value":{"type":"ENROLLED_OBJECT"}}],"object_type_id":"0-5","properties":[{"targetProperty":"subject","value":{"staticValue":"{{ enrolled_object.dealname }}","type":"STATIC_VALUE"}},{"targetProperty":"hs_pipeline_stage","value":{"staticValue":"1100007030","type":"STATIC_VALUE"}},{"targetProperty":"hubspot_owner_id","value":{"staticValue":"81929768","type":"STATIC_VALUE"}}],"use_explicit_associations":"true"},"type":"SINGLE_CONNECTION"}],"blockedDates":[],"enrollmentCriteria":{"listFilterBranch":{"filterBranchOperator":"OR","filterBranchType":"OR","filterBranches":[{"filterBranchOperator":"AND","filterBranchType":"AND","filterBranches":[],"filters":[{"filterType":"PROPERTY","operation":{"includeObjectsWithNoValueSet":false,"operationType":"ENUMERATION","operator":"IS_ANY_OF","values":["150102819"]},"property":"dealstage"}]}],"filters":[]},"reEnrollmentTriggersFilterBranches":[],"shouldReEnroll":false,"type":"LIST_BASED","unEnrollObjectsNotMeetingCriteria":false},"id":"1670039203","isEnabled":true,"name":"Closed Won | Create Ticket in INITIAL SETUP - UNASSIGNED","objectTypeId":"0-3","revisionId":"14","startActionId":"1","timeWindows":[],"updatedAt":"2026-10-08T11:35:19.692Z"}</t>
         </is>
       </c>
     </row>
